--- a/specifications/Test Requirements & Assessment Index.xlsx
+++ b/specifications/Test Requirements & Assessment Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenScenario\test_assets\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="488" documentId="13_ncr:1_{F5A69BD8-62CC-4032-9E11-682A20827548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57FD235A-1879-4CA6-92D3-28DE2916D243}"/>
+  <xr:revisionPtr revIDLastSave="630" documentId="13_ncr:1_{F5A69BD8-62CC-4032-9E11-682A20827548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{616AB501-4605-4C72-8F46-50223CDEE7E7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0. SUM" sheetId="3" r:id="rId1"/>
@@ -25,10 +25,12 @@
     <sheet name="9. DOW" sheetId="11" r:id="rId10"/>
     <sheet name="10. RCTA" sheetId="12" r:id="rId11"/>
     <sheet name="11. IA" sheetId="13" r:id="rId12"/>
+    <sheet name="16. RAEB" sheetId="14" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. ACC'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6. LKA'!$B$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16. RAEB'!$B$2:$F$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="489">
   <si>
     <t>Feature list</t>
   </si>
@@ -131,30 +133,196 @@
     <t>Door Open Warning</t>
   </si>
   <si>
+    <r>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Meaning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
     <t>RCTA</t>
   </si>
   <si>
     <t>Rear Cross Traffic Alert</t>
   </si>
   <si>
+    <r>
+      <t>Functional Behavior</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <t>Verifies that the feature performs its intended core functions according to the specification​</t>
+  </si>
+  <si>
     <t>IA</t>
   </si>
   <si>
     <t>Intersection Assist</t>
   </si>
   <si>
+    <r>
+      <t>State &amp; Mode Stability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <t>Verifies stability and correctness of state and mode transitions​</t>
+  </si>
+  <si>
     <t>FPA</t>
   </si>
   <si>
     <t>Front Parking Assist</t>
   </si>
   <si>
+    <r>
+      <t>Steady‑State Performance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <t>Evaluates performance of the behavior under stable operating conditions (software‑driven, HW‑independent)​</t>
+  </si>
+  <si>
     <t>RPA</t>
   </si>
   <si>
     <t>Rear Parking Assist</t>
   </si>
   <si>
+    <r>
+      <t>Logical Robustness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <charset val="1"/>
+      </rPr>
+      <t>​</t>
+    </r>
+  </si>
+  <si>
+    <t>Verifies correct logical behavior under boundary or edge‑case conditions​</t>
+  </si>
+  <si>
     <t>FCW</t>
   </si>
   <si>
@@ -212,7 +380,7 @@
     <t>KPI</t>
   </si>
   <si>
-    <t>REQ_ACC_001</t>
+    <t>ACC_REQ_001</t>
   </si>
   <si>
     <t>ACC Modes - Cruise Control Mode</t>
@@ -230,7 +398,7 @@
     <t>- Speed stability: +/-1 kph on the flat road, +/-3 kph on the slope</t>
   </si>
   <si>
-    <t>REQ_ACC_002</t>
+    <t>ACC_REQ_002</t>
   </si>
   <si>
     <t>ACC Modes - Follow Mode</t>
@@ -248,7 +416,7 @@
 - Logic: no crashing (eg: gap distance &gt;2m)</t>
   </si>
   <si>
-    <t>REQ_ACC_003</t>
+    <t>ACC_REQ_003</t>
   </si>
   <si>
     <t>ACC Modes - Bend limit Mode</t>
@@ -263,7 +431,7 @@
 - Logic: reduce speed on required range (table in spec)</t>
   </si>
   <si>
-    <t>REQ_ACC_004</t>
+    <t>ACC_REQ_004</t>
   </si>
   <si>
     <t>ACC Modes - Overtaking Mode</t>
@@ -276,7 +444,7 @@
 - Logic: speed up  when start overtaking</t>
   </si>
   <si>
-    <t>REQ_ACC_005</t>
+    <t>ACC_REQ_005</t>
   </si>
   <si>
     <t>ACC shall be able to recognize a stationary vehicle and decelerate without triggering the FWC/AEB if ego vehicle speed</t>
@@ -289,7 +457,7 @@
 - Logic: speed down when detected stop TV</t>
   </si>
   <si>
-    <t>REQ_ACC_006</t>
+    <t>ACC_REQ_006</t>
   </si>
   <si>
     <t>ACC shall drive off automatically after full stop if the lead vehicle drives off within</t>
@@ -305,7 +473,7 @@
 - Logic: no crashing (eg: gap distance &gt;2m)</t>
   </si>
   <si>
-    <t>REQ_ACC_007</t>
+    <t>ACC_REQ_007</t>
   </si>
   <si>
     <t>ACC will be cancelled if ACC has followed leading vehicle to stop for</t>
@@ -314,7 +482,7 @@
     <t>&gt;= 5 min</t>
   </si>
   <si>
-    <t>REQ_ACC_008</t>
+    <t>ACC_REQ_008</t>
   </si>
   <si>
     <t>The driver can resume ACC feature using resume button or tap on the gas pedal, if the vehicle is at stop between</t>
@@ -329,7 +497,7 @@
 - Logic: no crashing (eg: gap distance &gt;2m)</t>
   </si>
   <si>
-    <t>REQ_ACC_009</t>
+    <t>ACC_REQ_009</t>
   </si>
   <si>
     <t>ACC Set Speed Control Accuracy for horizontal roads</t>
@@ -344,7 +512,7 @@
     <t>Combine with REQ_ACC_001</t>
   </si>
   <si>
-    <t>REQ_ACC_010</t>
+    <t>ACC_REQ_010</t>
   </si>
   <si>
     <t>ACC Set Speed Control Accuracy for slope roads</t>
@@ -353,7 +521,7 @@
     <t>&lt;= 3 km/h</t>
   </si>
   <si>
-    <t>REQ_ACC_011</t>
+    <t>ACC_REQ_011</t>
   </si>
   <si>
     <t>The speed range of ego vehicle for ACC system to work shall be</t>
@@ -368,7 +536,7 @@
     <t>ACC works at speed =150kph (Stop mode test at speed=0)</t>
   </si>
   <si>
-    <t>REQ_ACC_012</t>
+    <t>ACC_REQ_012</t>
   </si>
   <si>
     <t>The speed range of ego vehicle for ACC system to be activated first time by pressing the Set-Speed (STANDBY -&gt; ACTIVE)</t>
@@ -383,13 +551,13 @@
     <t>System chage state as requirement description</t>
   </si>
   <si>
-    <t>REQ_ACC_013</t>
+    <t>ACC_REQ_013</t>
   </si>
   <si>
     <t>0- 150 kph (with target)</t>
   </si>
   <si>
-    <t>REQ_ACC_014</t>
+    <t>ACC_REQ_014</t>
   </si>
   <si>
     <t>ACC can be resumed at any speed</t>
@@ -398,7 +566,7 @@
     <t>0- 150 kph</t>
   </si>
   <si>
-    <t>REQ_ACC_015</t>
+    <t>ACC_REQ_015</t>
   </si>
   <si>
     <t>When vehicle is traveling over 72 kph, ACC automatic deceleration shall</t>
@@ -407,7 +575,7 @@
     <t>not exceed 3.5 m/s^2 (average over 2 sec)</t>
   </si>
   <si>
-    <t>REQ_ACC_016</t>
+    <t>ACC_REQ_016</t>
   </si>
   <si>
     <t>When vehicle is traveling below 18 kph, ACC automatic deceleration shall</t>
@@ -416,7 +584,7 @@
     <t>not exceed 5.0 m/s^2 (average over 2 sec)</t>
   </si>
   <si>
-    <t>REQ_ACC_017</t>
+    <t>ACC_REQ_017</t>
   </si>
   <si>
     <t>When vehicle is traveling over 72 kph, ACC automatic acceleration shall</t>
@@ -425,7 +593,7 @@
     <t>not exceed 2.0 m/s^2 (average over 2 sec)</t>
   </si>
   <si>
-    <t>REQ_ACC_018</t>
+    <t>ACC_REQ_018</t>
   </si>
   <si>
     <t>When vehicle is traveling below 18 kph, ACC automatic acceleration shall</t>
@@ -434,7 +602,7 @@
     <t>not exceed 4.0 m/s^2 (average over 2 sec)</t>
   </si>
   <si>
-    <t>REQ_ACC_019</t>
+    <t>ACC_REQ_019</t>
   </si>
   <si>
     <t>When vehicle is traveling over 72 kph, ACC average rate of change of automatic deceleration (negative jerk) shall</t>
@@ -443,7 +611,7 @@
     <t>not exceed 2.5 m/s^3(average over 1 sec)</t>
   </si>
   <si>
-    <t>REQ_ACC_020</t>
+    <t>ACC_REQ_020</t>
   </si>
   <si>
     <t>When vehicle is traveling below 18 kph, ACC average rate of change of automatic deceleration (negative jerk) shall</t>
@@ -452,7 +620,7 @@
     <t>not exceed 5.0 m/s^3 (average over 1 sec)</t>
   </si>
   <si>
-    <t>REQ_ACC_021</t>
+    <t>ACC_REQ_021</t>
   </si>
   <si>
     <t>ACC shall work on curved roads with radius</t>
@@ -462,7 +630,7 @@
 ACC may work with smaller Radius, because ACC with intelligent Curving mode could control the vehicle speed according the radius of lane (Check next KPI)</t>
   </si>
   <si>
-    <t>REQ_ACC_022</t>
+    <t>ACC_REQ_022</t>
   </si>
   <si>
     <t>ACC shall follow the front car stop and go behavior in the following slope range</t>
@@ -471,7 +639,7 @@
     <t>Performance guaranteed within ±15%</t>
   </si>
   <si>
-    <t>REQ_ACC_023</t>
+    <t>ACC_REQ_023</t>
   </si>
   <si>
     <t>When the ACC any button is pressed, signal will be received with higher frequency
@@ -481,7 +649,7 @@
     <t>3 cycles with 50ms cycle time</t>
   </si>
   <si>
-    <t>REQ_ACC_024</t>
+    <t>ACC_REQ_024</t>
   </si>
   <si>
     <t>When button released or after 3 cycles signals will come back to lower frequency
@@ -491,7 +659,7 @@
     <t>1000ms cycle time</t>
   </si>
   <si>
-    <t>REQ_ACC_025</t>
+    <t>ACC_REQ_025</t>
   </si>
   <si>
     <t>Short press of SPEED+ button ACC will increase speed by</t>
@@ -500,13 +668,13 @@
     <t>1 mph</t>
   </si>
   <si>
-    <t>REQ_ACC_026</t>
+    <t>ACC_REQ_026</t>
   </si>
   <si>
     <t>Short press of SPEED- button ACC will decrease speed by</t>
   </si>
   <si>
-    <t>REQ_ACC_027</t>
+    <t>ACC_REQ_027</t>
   </si>
   <si>
     <t>Long press of SPEED+ button ACC will increase speed by</t>
@@ -515,7 +683,7 @@
     <t>5 mph, frequency is 2 Hz (2 increases per second)</t>
   </si>
   <si>
-    <t>REQ_ACC_028</t>
+    <t>ACC_REQ_028</t>
   </si>
   <si>
     <t>Long press of SPEED- button ACC will decrease speed by</t>
@@ -524,7 +692,7 @@
     <t>5 mph, frequency is 2 Hz (2 decreases per second)</t>
   </si>
   <si>
-    <t>REQ_ACC_029</t>
+    <t>ACC_REQ_029</t>
   </si>
   <si>
     <t>With 1st level to 4th level Gap distances, the time to the impeding vehicle shall be</t>
@@ -533,7 +701,7 @@
     <t>1 - 2 seconds</t>
   </si>
   <si>
-    <t>REQ_ACC_030</t>
+    <t>ACC_REQ_030</t>
   </si>
   <si>
     <t>If Camera failsafe detected, ACC should be deactivated if host speed</t>
@@ -542,7 +710,7 @@
     <t>&lt;20kph</t>
   </si>
   <si>
-    <t>REQ_ACC_031</t>
+    <t>ACC_REQ_031</t>
   </si>
   <si>
     <t>ACC system will request the driver to take over if all of these conditions are satisfied:</t>
@@ -554,7 +722,7 @@
 4. None of the system limit warning suppressions is active.</t>
   </si>
   <si>
-    <t>REQ_ACC_032</t>
+    <t>ACC_REQ_032</t>
   </si>
   <si>
     <t>ACC system will continuously request the driver to take over if one of these conditions ais satisfied
@@ -577,7 +745,7 @@
 14. Go Displacement Limitation Check failed (Longer than 1.6m within 1.5s)</t>
   </si>
   <si>
-    <t>REQ_ACC_033</t>
+    <t>ACC_REQ_033</t>
   </si>
   <si>
     <t>ACC system will transfer from ACTIVE to PASSIVE (ACC not controlling the vehicle) if one of these conditions is detected:
@@ -597,7 +765,7 @@
 11. Steering Angle Sensor (SAS) not calibrated</t>
   </si>
   <si>
-    <t>REQ_ACC_034</t>
+    <t>ACC_REQ_034</t>
   </si>
   <si>
     <t>ACC system will transfer from ACTIVE to STANDBY (Ready to be active if one of these conditions is detected:
@@ -607,7 +775,7 @@
     <t>1. Press the Cancel button</t>
   </si>
   <si>
-    <t>REQ_ACC_035</t>
+    <t>ACC_REQ_035</t>
   </si>
   <si>
     <t>ACC shall drive off automatically after full stop if all these conditions are satisfied</t>
@@ -622,7 +790,7 @@
 exists</t>
   </si>
   <si>
-    <t>REQ_ACC_036</t>
+    <t>ACC_REQ_036</t>
   </si>
   <si>
     <t>System shall request driver to take over if all conditions are met:</t>
@@ -637,7 +805,7 @@
 none of the system limit warning suppressions is active</t>
   </si>
   <si>
-    <t>REQ_ACC_037</t>
+    <t>ACC_REQ_037</t>
   </si>
   <si>
     <t>System shall request driver to take over if one of these conditions is detected:</t>
@@ -662,7 +830,7 @@
 17. Driver presses brake pedal, Driver pressing gas pedal</t>
   </si>
   <si>
-    <t>REQ_ACC_038</t>
+    <t>ACC_REQ_038</t>
   </si>
   <si>
     <t>Sysetm shall no longer request driver to take over if</t>
@@ -671,7 +839,7 @@
     <t>Driver presses brake pedal, Driver pressing gas pedal</t>
   </si>
   <si>
-    <t>REQ_ACC_039</t>
+    <t>ACC_REQ_039</t>
   </si>
   <si>
     <t>System shall transfer from Off to Passive state if one of these conditions is detected:</t>
@@ -703,7 +871,7 @@
 24. Camera failsafe detected and host speed &lt;20kph</t>
   </si>
   <si>
-    <t>REQ_ACC_040</t>
+    <t>ACC_REQ_040</t>
   </si>
   <si>
     <t>System shall transfer from Off state to Failure state if</t>
@@ -712,7 +880,7 @@
     <t>any ACC system fault is detected</t>
   </si>
   <si>
-    <t>REQ_ACC_041</t>
+    <t>ACC_REQ_041</t>
   </si>
   <si>
     <t>System shall transfer from any Other state to Off state if</t>
@@ -721,7 +889,7 @@
     <t>IGN OFF</t>
   </si>
   <si>
-    <t>REQ_ACC_042</t>
+    <t>ACC_REQ_042</t>
   </si>
   <si>
     <t>System shall transfer from Passive state to Standby state if</t>
@@ -730,13 +898,13 @@
     <t>no inhibit condition detected</t>
   </si>
   <si>
-    <t>REQ_ACC_043</t>
+    <t>ACC_REQ_043</t>
   </si>
   <si>
     <t>System shall transfer from Passive state to Failure state if</t>
   </si>
   <si>
-    <t>REQ_ACC_044</t>
+    <t>ACC_REQ_044</t>
   </si>
   <si>
     <t>System shall transfer from Standby state to Passive state if any of the following conditions is met:</t>
@@ -745,7 +913,7 @@
     <t>Inhibit conditions in 5.1.1</t>
   </si>
   <si>
-    <t>REQ_ACC_045</t>
+    <t>ACC_REQ_045</t>
   </si>
   <si>
     <t>ACC changes from Standby to Active Control State if all these conditions are satisfied:</t>
@@ -758,7 +926,7 @@
 5. Standby State, and 20kph ≤ vset ≤ 150kph, and v ≤ 150kph, and Press RESUME button</t>
   </si>
   <si>
-    <t>REQ_ACC_046</t>
+    <t>ACC_REQ_046</t>
   </si>
   <si>
     <t>System shall transfer from Standby to Standstill Active state if all conditions are met:</t>
@@ -775,7 +943,7 @@
 If ACC function has been activated in current ignition cycle (then system has set speed), ACC can be resumed at standstill with or without leading vehicle)</t>
   </si>
   <si>
-    <t>REQ_ACC_047</t>
+    <t>ACC_REQ_047</t>
   </si>
   <si>
     <t>System shall transfer from Standby state to Failure state if</t>
@@ -784,7 +952,7 @@
     <t>Any ACC system fault is detected</t>
   </si>
   <si>
-    <t>REQ_ACC_048</t>
+    <t>ACC_REQ_048</t>
   </si>
   <si>
     <t>System shall transfer from Active to Passive state if one of these conditions is detected:</t>
@@ -803,7 +971,7 @@
 11. Camera failsafe detected and host speed &lt;20kph</t>
   </si>
   <si>
-    <t>REQ_ACC_049</t>
+    <t>ACC_REQ_049</t>
   </si>
   <si>
     <t>System shall transfer from Active to Standby state</t>
@@ -812,7 +980,7 @@
     <t>Press CANCEL button</t>
   </si>
   <si>
-    <t>REQ_ACC_050</t>
+    <t>ACC_REQ_050</t>
   </si>
   <si>
     <t>System shall transfer from Active to Brake Only if one of these conditions is detected:</t>
@@ -828,7 +996,7 @@
 8. ACC target lost in near range</t>
   </si>
   <si>
-    <t>REQ_ACC_051</t>
+    <t>ACC_REQ_051</t>
   </si>
   <si>
     <t>System shall transfer from Active or Standstill Active to Override state</t>
@@ -839,7 +1007,7 @@
 --&gt; VUT accelerates</t>
   </si>
   <si>
-    <t>REQ_ACC_052</t>
+    <t>ACC_REQ_052</t>
   </si>
   <si>
     <t>System shall transfer from Active to Standstill Active state if all conditions are met:</t>
@@ -854,13 +1022,13 @@
 Brake pedal is not pressed</t>
   </si>
   <si>
-    <t>REQ_ACC_053</t>
+    <t>ACC_REQ_053</t>
   </si>
   <si>
     <t>System shall transfer from Active state to Failure Mode state if</t>
   </si>
   <si>
-    <t>REQ_ACC_054</t>
+    <t>ACC_REQ_054</t>
   </si>
   <si>
     <t>System shall transfer from Override to Active state</t>
@@ -869,7 +1037,7 @@
     <t>Release acceleration pedal</t>
   </si>
   <si>
-    <t>REQ_ACC_055</t>
+    <t>ACC_REQ_055</t>
   </si>
   <si>
     <t>System shall transfer from Override to Passive state if one of these conditions is detected:</t>
@@ -879,7 +1047,7 @@
 2. Activate Auto parking system</t>
   </si>
   <si>
-    <t>REQ_ACC_056</t>
+    <t>ACC_REQ_056</t>
   </si>
   <si>
     <t>System shall transfer from Override state to Brake Only if one of these conditions is detected:</t>
@@ -903,13 +1071,13 @@
 16. ACC target lost suddenly in near range</t>
   </si>
   <si>
-    <t>REQ_ACC_057</t>
+    <t>ACC_REQ_057</t>
   </si>
   <si>
     <t>System shall transfer from Override state to Failure state if</t>
   </si>
   <si>
-    <t>REQ_ACC_058</t>
+    <t>ACC_REQ_058</t>
   </si>
   <si>
     <t>System shall transfer from Brake Only to Passive state if one of these conditions is detected:</t>
@@ -921,13 +1089,13 @@
 4. Driver override</t>
   </si>
   <si>
-    <t>REQ_ACC_059</t>
+    <t>ACC_REQ_059</t>
   </si>
   <si>
     <t>System shall transfer from Brake Only state to Failure Mode state if</t>
   </si>
   <si>
-    <t>REQ_ACC_060</t>
+    <t>ACC_REQ_060</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Active to Passive state if one of these conditions is detected:</t>
@@ -945,7 +1113,7 @@
 10. ACC target lost in near range</t>
   </si>
   <si>
-    <t>REQ_ACC_061</t>
+    <t>ACC_REQ_061</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Active to Active state and drive off if all conditions are met:</t>
@@ -962,7 +1130,7 @@
 (if the target vehicle exists, the relative distance between target vehicle and host vehicle &gt; 8.5m/s (could be calibrated), OR the relative distance &gt; 3.5m/s (could be calibrated) and relative speed &gt; 0.5m/s for certain time if the target vehicle exists)</t>
   </si>
   <si>
-    <t>REQ_ACC_062</t>
+    <t>ACC_REQ_062</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Active to Standstill Wait state if</t>
@@ -971,13 +1139,13 @@
     <t>Status of ‘standstill-active’ last longer than 3s</t>
   </si>
   <si>
-    <t>REQ_ACC_063</t>
+    <t>ACC_REQ_063</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Active state to Failure Mode state if</t>
   </si>
   <si>
-    <t>REQ_ACC_064</t>
+    <t>ACC_REQ_064</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Wait state to Passive state if one of these conditions is detected:</t>
@@ -1014,7 +1182,7 @@
 29. Duration time of Stand-Wait state over APV_Stl_Wait_Pas_Time (5 mins)</t>
   </si>
   <si>
-    <t>REQ_ACC_065</t>
+    <t>ACC_REQ_065</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Wait to Active state if all conditions met:</t>
@@ -1027,7 +1195,7 @@
 Brake pedal is not pressed</t>
   </si>
   <si>
-    <t>REQ_ACC_066</t>
+    <t>ACC_REQ_066</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Wait to Override state if</t>
@@ -1036,7 +1204,7 @@
     <t>acceleration pedal position is larger than the threshold</t>
   </si>
   <si>
-    <t>REQ_ACC_067</t>
+    <t>ACC_REQ_067</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Wait to Standstill Active state if all conditions are met:</t>
@@ -1049,13 +1217,13 @@
 Brake pedal is not pressed</t>
   </si>
   <si>
-    <t>REQ_ACC_068</t>
+    <t>ACC_REQ_068</t>
   </si>
   <si>
     <t>System shall transfer from Standstill Wait state to Failure Mode state if</t>
   </si>
   <si>
-    <t>REQ_ACC_069</t>
+    <t>ACC_REQ_069</t>
   </si>
   <si>
     <t>ACC shall inform the driver to take over if all conditions are met:</t>
@@ -1064,7 +1232,7 @@
     <t>Brake only State</t>
   </si>
   <si>
-    <t>REQ_ACC_070</t>
+    <t>ACC_REQ_070</t>
   </si>
   <si>
     <t>Potential collision has been registered which means cannot avoid collision with ACC deceleration
@@ -1076,7 +1244,7 @@
 None of the system limit warning suppressions is active.</t>
   </si>
   <si>
-    <t>REQ_ACC_071</t>
+    <t>ACC_REQ_071</t>
   </si>
   <si>
     <t>ACC shall suppress system limit warning if</t>
@@ -1085,7 +1253,7 @@
     <t>Driver takes the control through braking, or Driver takes the control through overriding</t>
   </si>
   <si>
-    <t>REQ_ACC_072</t>
+    <t>ACC_REQ_072</t>
   </si>
   <si>
     <t>ACC shall decelerate in advance of a curve</t>
@@ -1094,7 +1262,7 @@
     <t>according the radius of curvature lane width (lane information from camera)</t>
   </si>
   <si>
-    <t>REQ_ACC_073</t>
+    <t>ACC_REQ_073</t>
   </si>
   <si>
     <t>ACC Failure Rate</t>
@@ -1103,7 +1271,7 @@
     <t>For ACC function, during 100000 km one error may occur. (0.001%)</t>
   </si>
   <si>
-    <t>REQ_ACC_074</t>
+    <t>ACC_REQ_074</t>
   </si>
   <si>
     <t>1. TCS off
@@ -1624,12 +1792,323 @@
 the system shall not display any LKA popup.
 FCAM_LA_popup = 0x0 (No Popup)</t>
   </si>
+  <si>
+    <t>RAEB_REQ_001</t>
+  </si>
+  <si>
+    <t>AEB host vehicle speed range if target is Moving vehicles:</t>
+  </si>
+  <si>
+    <t>5 - 130 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_002</t>
+  </si>
+  <si>
+    <t>AEB host vehicle speed range if target is Stationary vehicles:</t>
+  </si>
+  <si>
+    <t>5 - 80 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_003</t>
+  </si>
+  <si>
+    <t>AEB host vehicle speed range if target is Moving VRU (Vulnerable Road User):</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_004</t>
+  </si>
+  <si>
+    <t>AEB host vehicle speed range if target is Stationary VRU</t>
+  </si>
+  <si>
+    <t>5 - 60 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_005</t>
+  </si>
+  <si>
+    <t>AEB host vehicle speed range if target is Crossing VRU</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEB supported deceleration </t>
+  </si>
+  <si>
+    <t>&lt;= 9 m/s^2</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_007</t>
+  </si>
+  <si>
+    <t>AEB shall be active when the TCC (Time to collision) is below the threshold</t>
+  </si>
+  <si>
+    <t>Check TTC (Time to collision) table to the right</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_008</t>
+  </si>
+  <si>
+    <t>AEB Maximum Speed Reduction (In order to prevent rear end collision) if target is vehicles</t>
+  </si>
+  <si>
+    <t>50 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_009</t>
+  </si>
+  <si>
+    <t>AEB Maximum Speed Reduction (In order to prevent rear end collision) if target is VRU (Vulnerable Road User)</t>
+  </si>
+  <si>
+    <t>40 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_010</t>
+  </si>
+  <si>
+    <t>AEB Intervention can be triggered if the last AEB intervention brake ending is longer than</t>
+  </si>
+  <si>
+    <t>[calibration] (default: 10s)</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEB shall work </t>
+  </si>
+  <si>
+    <t>based on detected licensable motor vehicles intended for use on public roads, i.e. motorcycles, cars, light trucks, buses, motor coaches, and other heavy vehicles.</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_012</t>
+  </si>
+  <si>
+    <t>JA shall be active when the TCC (Time to collision) is below the threshold</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_013</t>
+  </si>
+  <si>
+    <t>JA Object vehicle speed condition</t>
+  </si>
+  <si>
+    <t>20 - 60 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_014</t>
+  </si>
+  <si>
+    <t>JA host vehicle operation speed range</t>
+  </si>
+  <si>
+    <t>8 - 30 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JA supported deceleration </t>
+  </si>
+  <si>
+    <t>RAEB_REQ_016</t>
+  </si>
+  <si>
+    <t>JA Maximum Speed Reduction</t>
+  </si>
+  <si>
+    <t>30 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_017</t>
+  </si>
+  <si>
+    <t>JA Object types</t>
+  </si>
+  <si>
+    <t>Vehicle, bicycle, pedestrian</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEB can be deactivated manually only when speed </t>
+  </si>
+  <si>
+    <t>&lt; 10 kph</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_019</t>
+  </si>
+  <si>
+    <t>AEB Overhead discrimination</t>
+  </si>
+  <si>
+    <t>AEB shall not activate braking based on the detection of overhead targets at a height greater than 4.5 m above the roadway</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_020</t>
+  </si>
+  <si>
+    <t>Brake light control</t>
+  </si>
+  <si>
+    <t>The brake lights shall be illuminated within 350 ms after AEB initiates the automatic service brake.</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_021</t>
+  </si>
+  <si>
+    <t>When the system has detected the possibility of an imminent collision</t>
+  </si>
+  <si>
+    <t>AEB shall be a braking demand of at least 5.0 m/s² to the service braking system of the vehicle.</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_022</t>
+  </si>
+  <si>
+    <t>AEB Failure Rate</t>
+  </si>
+  <si>
+    <t>For AEB function, during 100000 km one error may occur (0.001%)</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_023</t>
+  </si>
+  <si>
+    <t>When the AEBS has detected the possibility of a collision with a pedestrian crossing the road at a constant speed of 5 km/h.</t>
+  </si>
+  <si>
+    <t>A collision warning shall be provided and shall be provided no later than the start of emergency braking intervention.</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_024</t>
+  </si>
+  <si>
+    <t>there shall be a braking demand of at least 5.0 m/s² to the service braking system of the vehicle.</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_025</t>
+  </si>
+  <si>
+    <t>AEB shall initiate appropriate FVCMS countermeasures when</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> the lateral offset is less than 20 %, even if part of the target vehicle is occluded from subject vehicle sensors;</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_026</t>
+  </si>
+  <si>
+    <t>AEB subject vehicle operation speed Vmin</t>
+  </si>
+  <si>
+    <t>30 kph (8,4 m/s) or less (this is the highest minimum value)</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_027</t>
+  </si>
+  <si>
+    <t>AEB subject vehicle operation speed Vmax</t>
+  </si>
+  <si>
+    <t>100 kph (27,8 m/s) or greater (this is the lowest maximum value)</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_028</t>
+  </si>
+  <si>
+    <t>AEB target vehicle operation speed Vmin</t>
+  </si>
+  <si>
+    <t>less than or equal 4.2 m/s = 15 kph 
+(AEB shall remain  functional while the target vehicle reduces its speed to 0 m/s)</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_029</t>
+  </si>
+  <si>
+    <t>AEB target vehicle operation speed Vmax</t>
+  </si>
+  <si>
+    <t>Vmax less the minimum relative velocity (KPI 73)</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_030</t>
+  </si>
+  <si>
+    <t>AEB Maximum lateral offset (lateral discrimination)</t>
+  </si>
+  <si>
+    <t>AEB shall function when the lateral offset is 20 % or lower in either direction. AEB may function for lateral offsets greater than 20 % at the discretion of the manufacturer.</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_031</t>
+  </si>
+  <si>
+    <t>AEB Maximum lateral speed</t>
+  </si>
+  <si>
+    <t>AEB shall function for relative vehicle lateral speeds of less than 0.2 m/s</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_032</t>
+  </si>
+  <si>
+    <t>AEB allowed conditions</t>
+  </si>
+  <si>
+    <t>1. The gear position is in one of "D" / "1" / "2" / "3" / "4" / "5" / "6" /"7" / "8" / "9" / "N".
+2. The FL/FR/RL/RR doors, trunk and bonnet open state is closed
+3. The Driver seatbelt buckled state is buckled.
+4. The acceleration pedal is pressed less than [calibration] (default: 80%)
+5. The current acceleration pedal change ratio compared with internal filtered acceleration pedal is less than [calibration] (default: 50%)
+6. The steering angle is less than [calibration] (default: 90 degree).
+7. The steering angle speed is less than [calibration] (default: 90 degree/s).</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_033</t>
+  </si>
+  <si>
+    <t>AEB cancel conditions</t>
+  </si>
+  <si>
+    <t>1. The acceleration pedal is pressed greater than [calibration] (default: 80%)
+2. The current acceleration pedal change ratio compared with internal filtered acceleration pedal is greater than [calibration] (default: 50%)
+3. The steering angle is greater than [calibration] (default: 90 degree).
+4. The steering angle speed is greater than [calibration] (default: 90 degree/s).</t>
+  </si>
+  <si>
+    <t>RAEB_REQ_034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEB shall transition to the OFF state. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upon turning the ignition to the off position, </t>
+  </si>
+  <si>
+    <t>RAEB_REQ_035</t>
+  </si>
+  <si>
+    <t>AEB enter the INACTIVE State if</t>
+  </si>
+  <si>
+    <t>1- The ignition cycle has been completed and the engine is running
+2- conditions for activating are not met(Park selected, Speed condition, .etc.)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1680,8 +2159,37 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1748,8 +2256,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF215F9A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1850,11 +2370,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1903,9 +2464,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1971,6 +2529,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1982,6 +2583,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1998,6 +2602,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A047CF8-5E94-CC36-00FE-AD7D3171F64D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12630150" y="2152650"/>
+          <a:ext cx="4572000" cy="590550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2268,21 +2921,22 @@
   <cols>
     <col min="4" max="4" width="33.140625" customWidth="1"/>
     <col min="5" max="5" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="9" max="9" width="64" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="G2" s="41" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="G2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="11" t="s">
@@ -2429,64 +3083,109 @@
         <v>25</v>
       </c>
       <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="2:9">
+      <c r="G12" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="29.25">
       <c r="B13" s="2">
         <v>10</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="2:9">
+      <c r="G13" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="29.25">
       <c r="B14" s="2">
         <v>11</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="2:9">
+      <c r="G14" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="30.75">
       <c r="B15" s="2">
         <v>12</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="2:9">
+      <c r="G15" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="30.75">
       <c r="B16" s="2">
         <v>13</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E16" s="3"/>
+      <c r="G16" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="2">
         <v>14</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E17" s="3"/>
     </row>
@@ -2495,10 +3194,10 @@
         <v>15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3"/>
     </row>
@@ -2507,10 +3206,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E19" s="3"/>
     </row>
@@ -2519,10 +3218,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -2531,10 +3230,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E21" s="3"/>
     </row>
@@ -2543,10 +3242,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E22" s="3"/>
     </row>
@@ -2555,10 +3254,10 @@
         <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3"/>
     </row>
@@ -2598,6 +3297,655 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F7F8D3-336A-4EB3-9234-66ADDFE3149E}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A2:F37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="55.28515625" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="20"/>
+      <c r="B2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30.75">
+      <c r="B3" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="46"/>
+    </row>
+    <row r="4" spans="1:6" ht="30.75">
+      <c r="B4" s="58" t="s">
+        <v>392</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>393</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>394</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="46"/>
+    </row>
+    <row r="5" spans="1:6" ht="30.75">
+      <c r="B5" s="58" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>394</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="46"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
+      <c r="B6" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>398</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>399</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="46"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
+      <c r="B7" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>399</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="46"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75">
+      <c r="B8" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="46"/>
+    </row>
+    <row r="9" spans="1:6" ht="30.75">
+      <c r="B9" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="46"/>
+    </row>
+    <row r="10" spans="1:6" ht="30.75">
+      <c r="B10" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>409</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="46"/>
+    </row>
+    <row r="11" spans="1:6" ht="46.5">
+      <c r="B11" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>412</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="46"/>
+    </row>
+    <row r="12" spans="1:6" ht="30.75">
+      <c r="B12" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>415</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>416</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="46"/>
+    </row>
+    <row r="13" spans="1:6" ht="46.5">
+      <c r="B13" s="58" t="s">
+        <v>417</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>418</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>419</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="46"/>
+    </row>
+    <row r="14" spans="1:6" ht="30.75">
+      <c r="B14" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="46"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75">
+      <c r="B15" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>424</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="46"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75">
+      <c r="B16" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="46"/>
+    </row>
+    <row r="17" spans="2:6" ht="15.75">
+      <c r="B17" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="46"/>
+    </row>
+    <row r="18" spans="2:6" ht="15.75">
+      <c r="B18" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>431</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>432</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="46"/>
+    </row>
+    <row r="19" spans="2:6" ht="15.75">
+      <c r="B19" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>435</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="46"/>
+    </row>
+    <row r="20" spans="2:6" ht="15.75">
+      <c r="B20" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>437</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>438</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="46"/>
+    </row>
+    <row r="21" spans="2:6" ht="46.5">
+      <c r="B21" s="58" t="s">
+        <v>439</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>440</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="46"/>
+    </row>
+    <row r="22" spans="2:6" ht="30.75">
+      <c r="B22" s="35" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>443</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="46"/>
+    </row>
+    <row r="23" spans="2:6" ht="30.75">
+      <c r="B23" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>446</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>447</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="46"/>
+    </row>
+    <row r="24" spans="2:6" ht="30.75">
+      <c r="B24" s="35" t="s">
+        <v>448</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>449</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="46"/>
+    </row>
+    <row r="25" spans="2:6" ht="46.5">
+      <c r="B25" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>452</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>453</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="46"/>
+    </row>
+    <row r="26" spans="2:6" ht="30.75">
+      <c r="B26" s="35" t="s">
+        <v>454</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>446</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>455</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="46"/>
+    </row>
+    <row r="27" spans="2:6" ht="30.75">
+      <c r="B27" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>457</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="46"/>
+    </row>
+    <row r="28" spans="2:6" ht="15.75">
+      <c r="B28" s="35" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>461</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="46"/>
+    </row>
+    <row r="29" spans="2:6" ht="15.75">
+      <c r="B29" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>463</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>464</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="46"/>
+    </row>
+    <row r="30" spans="2:6" ht="61.5">
+      <c r="B30" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>466</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>467</v>
+      </c>
+      <c r="E30" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="46"/>
+    </row>
+    <row r="31" spans="2:6" ht="15.75">
+      <c r="B31" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>469</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>470</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="46"/>
+    </row>
+    <row r="32" spans="2:6" ht="46.5">
+      <c r="B32" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>472</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>473</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="46"/>
+    </row>
+    <row r="33" spans="2:6" ht="30.75">
+      <c r="B33" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C33" s="52" t="s">
+        <v>475</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>476</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="46"/>
+    </row>
+    <row r="34" spans="2:6" ht="200.25">
+      <c r="B34" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>478</v>
+      </c>
+      <c r="D34" s="47" t="s">
+        <v>479</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" s="46"/>
+    </row>
+    <row r="35" spans="2:6" ht="138.75">
+      <c r="B35" s="35" t="s">
+        <v>480</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>481</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>482</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" s="46"/>
+    </row>
+    <row r="36" spans="2:6" ht="15.75">
+      <c r="B36" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="C36" s="50" t="s">
+        <v>484</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>485</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="46"/>
+    </row>
+    <row r="37" spans="2:6" ht="61.5">
+      <c r="B37" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="C37" s="50" t="s">
+        <v>487</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>488</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="46"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:F37" xr:uid="{51F7F8D3-336A-4EB3-9234-66ADDFE3149E}"/>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:D5 C7:D8">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:D17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C34:D35 C15:D16 C10:D12 D9 C18:D19">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6992B19-4DB5-4F87-87D1-7E5660A78B77}">
   <dimension ref="A1"/>
@@ -2615,1288 +3963,1288 @@
   <dimension ref="B2:F76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="22" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="86.5703125" style="22" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="22"/>
-    <col min="6" max="6" width="34.7109375" style="22" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="22"/>
+    <col min="1" max="1" width="5.5703125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="86.5703125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="21"/>
+    <col min="6" max="6" width="34.7109375" style="21" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" s="21" customFormat="1">
+    <row r="2" spans="2:6" s="20" customFormat="1">
       <c r="B2" s="13" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>52</v>
+        <v>65</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="115.5">
       <c r="B3" s="17" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>56</v>
+        <v>69</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="115.5">
       <c r="B4" s="17" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>61</v>
+        <v>75</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="72.75">
-      <c r="B5" s="18" t="s">
-        <v>62</v>
+      <c r="B5" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>65</v>
+        <v>79</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="57.75">
-      <c r="B6" s="18" t="s">
-        <v>66</v>
+      <c r="B6" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>69</v>
+        <v>83</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="57.75">
       <c r="B7" s="17" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>73</v>
+      <c r="F7" s="22" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="87">
-      <c r="B8" s="18" t="s">
-        <v>74</v>
+      <c r="B8" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>77</v>
+        <v>91</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="87">
       <c r="B9" s="17" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>77</v>
+        <v>95</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="72.75">
       <c r="B10" s="17" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>84</v>
+        <v>98</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="29.25">
       <c r="B11" s="17" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>88</v>
+        <v>102</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="29.25">
       <c r="B12" s="17" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>88</v>
+        <v>107</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="29.25">
       <c r="B13" s="17" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>96</v>
+        <v>110</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="57.75">
       <c r="B14" s="17" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>101</v>
+        <v>115</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="57.75">
       <c r="B15" s="17" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>101</v>
+        <v>119</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="29.25">
       <c r="B16" s="17" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>56</v>
+        <v>122</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="29.25">
       <c r="B17" s="17" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>88</v>
+        <v>125</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="29.25">
       <c r="B18" s="17" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>88</v>
+        <v>128</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="29.25">
       <c r="B19" s="17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>88</v>
+        <v>131</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="29.25">
       <c r="B20" s="17" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>88</v>
+        <v>134</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="43.5">
       <c r="B21" s="17" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>88</v>
+        <v>137</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="43.5">
       <c r="B22" s="17" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>88</v>
+        <v>140</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="43.5">
       <c r="B23" s="17" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>96</v>
+        <v>143</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="29.25">
       <c r="B24" s="17" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>96</v>
+        <v>146</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="72.75">
       <c r="B25" s="17" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>56</v>
+        <v>149</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="72.75">
       <c r="B26" s="17" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>56</v>
+        <v>152</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="29.25">
       <c r="B27" s="17" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>56</v>
+        <v>155</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="29.25">
       <c r="B28" s="17" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>56</v>
+        <v>155</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="29.25">
       <c r="B29" s="17" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>56</v>
+        <v>160</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="29.25">
       <c r="B30" s="17" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>56</v>
+        <v>163</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="29.25">
       <c r="B31" s="17" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>88</v>
+        <v>166</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="29.25">
       <c r="B32" s="17" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>101</v>
+        <v>169</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="57.75">
       <c r="B33" s="17" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>96</v>
+        <v>172</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="201.75">
       <c r="B34" s="17" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>96</v>
+        <v>175</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="159">
       <c r="B35" s="17" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>101</v>
+        <v>178</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="72.75">
       <c r="B36" s="17" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>101</v>
+        <v>181</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="130.5">
       <c r="B37" s="17" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>101</v>
+        <v>184</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="115.5">
       <c r="B38" s="17" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>96</v>
+        <v>187</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="245.25">
       <c r="B39" s="17" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>96</v>
+        <v>190</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="29.25">
       <c r="B40" s="17" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E40" s="25" t="s">
-        <v>96</v>
+        <v>193</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="2:6" ht="346.5">
       <c r="B41" s="17" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="E41" s="25" t="s">
-        <v>101</v>
+        <v>196</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="29.25">
       <c r="B42" s="17" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>101</v>
+        <v>199</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="29.25">
       <c r="B43" s="17" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="25" t="s">
-        <v>101</v>
+        <v>202</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="29.25">
       <c r="B44" s="17" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>101</v>
+        <v>205</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="29.25">
       <c r="B45" s="17" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>101</v>
+        <v>199</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="43.5">
       <c r="B46" s="17" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>101</v>
+        <v>210</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="101.25">
       <c r="B47" s="17" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>101</v>
+        <v>213</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="189.75">
       <c r="B48" s="17" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>101</v>
+        <v>216</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="29.25">
       <c r="B49" s="17" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>101</v>
+        <v>219</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="158.25" customHeight="1">
       <c r="B50" s="17" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="E50" s="25" t="s">
-        <v>101</v>
+        <v>222</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="29.25">
       <c r="B51" s="17" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="E51" s="25" t="s">
-        <v>101</v>
+        <v>225</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="115.5">
       <c r="B52" s="17" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>101</v>
+        <v>228</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="43.5">
       <c r="B53" s="17" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>101</v>
+        <v>231</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="101.25">
       <c r="B54" s="17" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>101</v>
+        <v>234</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="29.25">
       <c r="B55" s="17" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="E55" s="25" t="s">
-        <v>101</v>
+        <v>219</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="2:6" ht="29.25">
       <c r="B56" s="17" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="E56" s="25" t="s">
-        <v>101</v>
+        <v>239</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="43.5">
       <c r="B57" s="17" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="E57" s="25" t="s">
-        <v>101</v>
+        <v>242</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="2:6" ht="231">
       <c r="B58" s="17" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="E58" s="25" t="s">
-        <v>101</v>
+        <v>245</v>
+      </c>
+      <c r="E58" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="2:6" ht="29.25">
       <c r="B59" s="17" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="E59" s="25" t="s">
-        <v>101</v>
+        <v>219</v>
+      </c>
+      <c r="E59" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="57.75">
       <c r="B60" s="17" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>101</v>
+        <v>250</v>
+      </c>
+      <c r="E60" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="2:6" ht="29.25">
       <c r="B61" s="17" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>101</v>
+        <v>219</v>
+      </c>
+      <c r="E61" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="144.75">
       <c r="B62" s="17" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>101</v>
+        <v>255</v>
+      </c>
+      <c r="E62" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="2:6" ht="174">
       <c r="B63" s="17" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E63" s="25" t="s">
-        <v>101</v>
+        <v>258</v>
+      </c>
+      <c r="E63" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="2:6" ht="29.25">
       <c r="B64" s="17" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>101</v>
+        <v>261</v>
+      </c>
+      <c r="E64" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="2:6" ht="29.25">
       <c r="B65" s="17" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>101</v>
+        <v>219</v>
+      </c>
+      <c r="E65" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="409.6">
       <c r="B66" s="17" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>101</v>
+        <v>266</v>
+      </c>
+      <c r="E66" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="72.75">
       <c r="B67" s="17" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>101</v>
+        <v>269</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="29.25">
       <c r="B68" s="17" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="E68" s="25" t="s">
-        <v>101</v>
+        <v>272</v>
+      </c>
+      <c r="E68" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="2:6" ht="72.75">
       <c r="B69" s="17" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="E69" s="25" t="s">
-        <v>101</v>
+        <v>275</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="2:6" ht="29.25">
       <c r="B70" s="17" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>101</v>
+        <v>199</v>
+      </c>
+      <c r="E70" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="2:6" ht="29.25">
       <c r="B71" s="17" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="E71" s="25" t="s">
-        <v>96</v>
+        <v>280</v>
+      </c>
+      <c r="E71" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="2:6" ht="115.5">
       <c r="B72" s="17" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="E72" s="25" t="s">
-        <v>96</v>
+        <v>282</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>111</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="2:6" ht="29.25">
       <c r="B73" s="17" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="E73" s="25" t="s">
-        <v>101</v>
+        <v>285</v>
+      </c>
+      <c r="E73" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="29.25">
       <c r="B74" s="17" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>56</v>
+        <v>288</v>
+      </c>
+      <c r="E74" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="29.25">
       <c r="B75" s="17" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="E75" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
+      </c>
+      <c r="E75" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="390">
       <c r="B76" s="17" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="E76" s="25" t="s">
-        <v>101</v>
+        <v>293</v>
+      </c>
+      <c r="E76" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3934,516 +5282,518 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511864B5-0E87-4471-A838-521EBF6D60FB}">
-  <sheetPr filterMode="1"/>
+  <sheetPr filterMode="1">
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5" style="28" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" style="28" customWidth="1"/>
-    <col min="4" max="4" width="65" style="27" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" style="37" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="28"/>
+    <col min="1" max="1" width="5" style="27" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="65" style="26" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" style="36" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="27"/>
+      <c r="A2" s="26"/>
       <c r="B2" s="13" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="72.75">
-      <c r="B3" s="36" t="s">
-        <v>279</v>
+      <c r="B3" s="35" t="s">
+        <v>294</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>282</v>
+        <v>295</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="175.5">
-      <c r="B4" s="36" t="s">
-        <v>283</v>
+      <c r="B4" s="35" t="s">
+        <v>298</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>286</v>
+        <v>299</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="57.75">
-      <c r="B5" s="36" t="s">
-        <v>287</v>
+      <c r="B5" s="35" t="s">
+        <v>302</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>290</v>
+        <v>303</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="46.5">
-      <c r="B6" s="36" t="s">
-        <v>291</v>
+      <c r="B6" s="35" t="s">
+        <v>306</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>290</v>
+        <v>307</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="57.75">
-      <c r="B7" s="36" t="s">
-        <v>294</v>
+      <c r="B7" s="35" t="s">
+        <v>309</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>296</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>297</v>
+        <v>310</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="346.5" hidden="1">
-      <c r="B8" s="36" t="s">
-        <v>298</v>
+      <c r="B8" s="35" t="s">
+        <v>313</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>101</v>
+        <v>314</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>116</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="409.6" hidden="1">
-      <c r="B9" s="36" t="s">
-        <v>301</v>
+      <c r="B9" s="35" t="s">
+        <v>316</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>101</v>
+        <v>317</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>116</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="174" hidden="1">
-      <c r="B10" s="36" t="s">
-        <v>304</v>
+      <c r="B10" s="35" t="s">
+        <v>319</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>101</v>
+        <v>320</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>116</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="72.75" hidden="1">
-      <c r="B11" s="36" t="s">
-        <v>307</v>
+      <c r="B11" s="35" t="s">
+        <v>322</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>101</v>
+        <v>323</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>116</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="57.75">
-      <c r="B12" s="36" t="s">
-        <v>310</v>
+      <c r="B12" s="35" t="s">
+        <v>325</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>313</v>
+        <v>326</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="245.25">
-      <c r="B13" s="36" t="s">
-        <v>314</v>
+      <c r="B13" s="35" t="s">
+        <v>329</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>316</v>
+        <v>326</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="231" hidden="1">
-      <c r="B14" s="36" t="s">
-        <v>317</v>
+      <c r="B14" s="35" t="s">
+        <v>332</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>319</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>101</v>
+        <v>333</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>116</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="57.75" hidden="1">
-      <c r="B15" s="36" t="s">
-        <v>320</v>
+      <c r="B15" s="35" t="s">
+        <v>335</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="38"/>
+        <v>336</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="37"/>
     </row>
     <row r="16" spans="1:8" ht="409.6" hidden="1">
-      <c r="B16" s="36" t="s">
-        <v>323</v>
+      <c r="B16" s="35" t="s">
+        <v>338</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>101</v>
+        <v>339</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>116</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="159" hidden="1">
-      <c r="B17" s="36" t="s">
-        <v>326</v>
+      <c r="B17" s="35" t="s">
+        <v>341</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="38"/>
+        <v>342</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="37"/>
     </row>
     <row r="18" spans="2:6" ht="181.5" hidden="1">
-      <c r="B18" s="36" t="s">
-        <v>329</v>
+      <c r="B18" s="35" t="s">
+        <v>344</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="38"/>
+        <v>345</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="E18" s="35"/>
+      <c r="F18" s="37"/>
     </row>
     <row r="19" spans="2:6" ht="88.5">
-      <c r="B19" s="36" t="s">
-        <v>332</v>
+      <c r="B19" s="35" t="s">
+        <v>347</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="38"/>
+        <v>348</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="37"/>
     </row>
     <row r="20" spans="2:6" ht="119.25">
-      <c r="B20" s="36" t="s">
-        <v>335</v>
+      <c r="B20" s="35" t="s">
+        <v>350</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="38"/>
+        <v>352</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="37"/>
     </row>
     <row r="21" spans="2:6" ht="233.25">
-      <c r="B21" s="36" t="s">
-        <v>338</v>
+      <c r="B21" s="35" t="s">
+        <v>353</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="38"/>
+        <v>355</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="37"/>
     </row>
     <row r="22" spans="2:6" ht="294.75">
-      <c r="B22" s="36" t="s">
-        <v>341</v>
+      <c r="B22" s="35" t="s">
+        <v>356</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="38"/>
+        <v>358</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="37"/>
     </row>
     <row r="23" spans="2:6" ht="144.75">
-      <c r="B23" s="36" t="s">
-        <v>344</v>
+      <c r="B23" s="35" t="s">
+        <v>359</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="38"/>
+        <v>361</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="37"/>
     </row>
     <row r="24" spans="2:6" ht="201.75">
-      <c r="B24" s="36" t="s">
-        <v>347</v>
+      <c r="B24" s="35" t="s">
+        <v>362</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="38"/>
+        <v>364</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="37"/>
     </row>
     <row r="25" spans="2:6" ht="188.25">
-      <c r="B25" s="36" t="s">
-        <v>350</v>
+      <c r="B25" s="35" t="s">
+        <v>365</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" s="38"/>
+        <v>367</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="37"/>
     </row>
     <row r="26" spans="2:6" ht="101.25">
-      <c r="B26" s="36" t="s">
-        <v>353</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>354</v>
+      <c r="B26" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>369</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="38"/>
+        <v>370</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="37"/>
     </row>
     <row r="27" spans="2:6" ht="101.25">
-      <c r="B27" s="36" t="s">
-        <v>356</v>
+      <c r="B27" s="35" t="s">
+        <v>371</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="38"/>
+        <v>372</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="37"/>
     </row>
     <row r="28" spans="2:6" ht="159">
-      <c r="B28" s="36" t="s">
-        <v>359</v>
+      <c r="B28" s="35" t="s">
+        <v>374</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>361</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="38"/>
+        <v>375</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="37"/>
     </row>
     <row r="29" spans="2:6" ht="57.75">
-      <c r="B29" s="36" t="s">
-        <v>362</v>
+      <c r="B29" s="35" t="s">
+        <v>377</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="38"/>
+        <v>378</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="37"/>
     </row>
     <row r="30" spans="2:6" ht="101.25">
-      <c r="B30" s="36" t="s">
-        <v>365</v>
+      <c r="B30" s="35" t="s">
+        <v>380</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="38"/>
+        <v>382</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="37"/>
     </row>
     <row r="31" spans="2:6" ht="72.75">
-      <c r="B31" s="36" t="s">
-        <v>368</v>
+      <c r="B31" s="35" t="s">
+        <v>383</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" s="38"/>
+        <v>385</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="37"/>
     </row>
     <row r="32" spans="2:6" ht="72.75">
-      <c r="B32" s="36" t="s">
-        <v>371</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="38"/>
+      <c r="B32" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:F32" xr:uid="{511864B5-0E87-4471-A838-521EBF6D60FB}">
